--- a/Libraries/Vehicle/Tire/MFMbody/sm_car_data_Tire_MFMbody.xlsx
+++ b/Libraries/Vehicle/Tire/MFMbody/sm_car_data_Tire_MFMbody.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Tire\MFMbody\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A836569-EA6E-4E68-A275-7AEEF02E17CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E7FB08-6BE1-4757-B5F6-821829A2F22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="2640" windowWidth="21555" windowHeight="11295" tabRatio="840" activeTab="2" xr2:uid="{038AE485-2DF6-4480-A05B-AFF15F06FE64}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="840" activeTab="7" xr2:uid="{038AE485-2DF6-4480-A05B-AFF15F06FE64}"/>
   </bookViews>
   <sheets>
     <sheet name="Tir_235_50R24" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="33">
   <si>
     <t>Units</t>
   </si>
@@ -67,9 +67,6 @@
     <t>tirFile</t>
   </si>
   <si>
-    <t>Inertia</t>
-  </si>
-  <si>
     <t>which('Bus_270_70R22.tir')</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
   </si>
   <si>
     <t>MFMbody</t>
-  </si>
-  <si>
-    <t>Mass</t>
   </si>
   <si>
     <t>MFMbody_190_50R10</t>
@@ -207,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -234,8 +228,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -250,63 +242,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill>
@@ -732,10 +668,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
@@ -744,7 +680,7 @@
     <col min="9" max="10" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -764,7 +700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -774,10 +710,10 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -786,10 +722,10 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
@@ -800,153 +736,122 @@
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="12"/>
+      <c r="H6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="14"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="14"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C16" s="16"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C17" s="16"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="C18" s="14"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C20" s="16"/>
-      <c r="H20" s="17"/>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C21" s="16"/>
-      <c r="H21" s="17"/>
+      <c r="C19" s="14"/>
+      <c r="H19" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A16:A21">
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+  <conditionalFormatting sqref="A14:A19 C4:D6 A4:A7">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+  <conditionalFormatting sqref="C7">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C19">
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 A4:A9">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+  <conditionalFormatting sqref="C14:C17">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -960,10 +865,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
@@ -972,7 +877,7 @@
     <col min="9" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -992,7 +897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1002,10 +907,10 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1014,10 +919,10 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
@@ -1028,113 +933,82 @@
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="12"/>
+      <c r="H6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="14"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="14"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="16"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="16"/>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="16"/>
-      <c r="H15" s="17"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="14"/>
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="14"/>
+      <c r="H13" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C9:C13">
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 A4:A15">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+  <conditionalFormatting sqref="C7:C11 C4:D6 A4:A13">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1147,10 +1021,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
@@ -1159,7 +1033,7 @@
     <col min="9" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1179,7 +1053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1189,10 +1063,10 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1201,10 +1075,10 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
@@ -1215,113 +1089,82 @@
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="12"/>
+      <c r="H6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="14"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="14"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="16"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="16"/>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="16"/>
-      <c r="H15" s="17"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="14"/>
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="14"/>
+      <c r="H13" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C9:C13">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 A4:A15">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="C7:C11 C4:D6 A4:A13">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1334,10 +1177,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
@@ -1346,7 +1189,7 @@
     <col min="9" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1366,7 +1209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1376,10 +1219,10 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1388,10 +1231,10 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
@@ -1402,128 +1245,97 @@
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="12"/>
+      <c r="H6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="14"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="14"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="16"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C12" s="16"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="16"/>
-      <c r="H15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C16" s="16"/>
-      <c r="H16" s="17"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="14"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="14"/>
+      <c r="H14" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A11:A16">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+  <conditionalFormatting sqref="A9:A14 C4:D6 A4:A7">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+  <conditionalFormatting sqref="C7">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C14">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 A4:A9">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+  <conditionalFormatting sqref="C9:C12">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1536,10 +1348,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
@@ -1548,7 +1360,7 @@
     <col min="9" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1568,7 +1380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1578,10 +1390,10 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1590,10 +1402,10 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
@@ -1604,113 +1416,82 @@
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="12"/>
+      <c r="H6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="14"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="14"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="16"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="16"/>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="16"/>
-      <c r="H15" s="17"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="14"/>
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="14"/>
+      <c r="H13" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C9:C13">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 A4:A15">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+  <conditionalFormatting sqref="C7:C11 C4:D6 A4:A13">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1724,10 +1505,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
@@ -1736,7 +1517,7 @@
     <col min="9" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1756,7 +1537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1766,10 +1547,10 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1778,10 +1559,10 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
@@ -1792,128 +1573,97 @@
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="12"/>
+      <c r="H6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="14"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="14"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="16"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C12" s="16"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="16"/>
-      <c r="H15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C16" s="16"/>
-      <c r="H16" s="17"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="14"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="14"/>
+      <c r="H14" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A11:A16">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+  <conditionalFormatting sqref="A9:A14 C4:D6 A4:A7">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+  <conditionalFormatting sqref="C7">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C14">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 A4:A9">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+  <conditionalFormatting sqref="C9:C12">
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1926,10 +1676,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
@@ -1968,7 +1718,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -1980,10 +1730,10 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="19"/>
-      <c r="N3" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="K3" s="17"/>
+      <c r="N3" s="17"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
@@ -1996,7 +1746,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -2006,72 +1756,56 @@
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="18" t="s">
-        <v>16</v>
+      <c r="H5" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <v>10</v>
+      <c r="G6" s="12"/>
+      <c r="H6" s="16" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
+      <c r="H8" s="13"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="13"/>
-      <c r="K10" s="19"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
@@ -2099,63 +1833,48 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C16" s="14"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C17" s="14"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C18" s="16"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C19" s="16"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="C20" s="14"/>
+      <c r="H20" s="15"/>
     </row>
     <row r="21" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C22" s="16"/>
-      <c r="H22" s="17"/>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C23" s="16"/>
-      <c r="H23" s="17"/>
+      <c r="C21" s="14"/>
+      <c r="H21" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A18:A23">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+  <conditionalFormatting sqref="A16:A21 C4:D6 A4:A8">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:C10">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+  <conditionalFormatting sqref="C7:C8">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:C21">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 A4:A10">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="C16:C19">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2168,10 +1887,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
@@ -2180,7 +1899,7 @@
     <col min="9" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -2200,7 +1919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -2210,10 +1929,10 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2222,10 +1941,10 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
@@ -2236,113 +1955,82 @@
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="12"/>
+      <c r="H6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="14"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="14"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="16"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="16"/>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="16"/>
-      <c r="H15" s="17"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="14"/>
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="14"/>
+      <c r="H13" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C9:C13">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 A4:A15">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+  <conditionalFormatting sqref="C7:C11 C4:D6 A4:A13">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
